--- a/wimoor-erp/erp-boot/src/main/resources/template/MaterialBaseInfo.xlsx
+++ b/wimoor-erp/erp-boot/src/main/resources/template/MaterialBaseInfo.xlsx
@@ -1,16 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23145" windowHeight="9675"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -18,6 +31,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
+    <author>liufei</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0">
@@ -42,12 +56,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="X1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>liufei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+是，否</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>SKU</t>
   </si>
@@ -89,6 +125,10 @@
   </si>
   <si>
     <t>负责人</t>
+  </si>
+  <si>
+    <t>是否使用
+子SKU成本</t>
   </si>
   <si>
     <t>长(cm)</t>
@@ -106,7 +146,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -739,7 +779,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -751,6 +791,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1106,7 +1149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1118,9 +1161,10 @@
     <col min="7" max="7" width="8.25" customWidth="1"/>
     <col min="10" max="10" width="6.5" customWidth="1"/>
     <col min="11" max="11" width="7.625" customWidth="1"/>
+    <col min="24" max="24" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1" spans="1:23">
+    <row r="1" ht="33" customHeight="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1172,52 +1216,56 @@
       <c r="W1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="X1" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
+    <row r="2" spans="1:24">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
         <v>15</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>16</v>
       </c>
-      <c r="K2" t="s">
+      <c r="N2" t="s">
         <v>17</v>
       </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" t="s">
-        <v>16</v>
-      </c>
       <c r="O2" t="s">
-        <v>17</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="X2" s="3"/>
     </row>
-    <row r="9" spans="16:16">
+    <row r="9" spans="1:24">
       <c r="P9" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="L1:O1"/>
@@ -1232,6 +1280,7 @@
     <mergeCell ref="U1:U2"/>
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="W1:W2"/>
+    <mergeCell ref="X1:X2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
